--- a/A/chrXI:0-47628_26_finemapping.xlsx
+++ b/A/chrXI:0-47628_26_finemapping.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3332" uniqueCount="3332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3324" uniqueCount="3324">
   <si>
     <t xml:space="preserve">seqnames</t>
   </si>
@@ -5150,7 +5150,7 @@
     <t xml:space="preserve">6/9</t>
   </si>
   <si>
-    <t xml:space="preserve">315/1978</t>
+    <t xml:space="preserve">323/1978</t>
   </si>
   <si>
     <t xml:space="preserve">YAL038W/YER081W/YGL253W/YHR174W/YHR216W/YJR009C</t>
@@ -9425,19 +9425,10 @@
     <t xml:space="preserve">in.hotspot</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.x</t>
-  </si>
-  <si>
     <t xml:space="preserve">bin_pos_l</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.y</t>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">chrom_short</t>
@@ -9699,21 +9690,6 @@
   </si>
   <si>
     <t xml:space="preserve">HBN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G2:M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_M:G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1:S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_S</t>
   </si>
   <si>
     <t xml:space="preserve">cis_fdr</t>
@@ -10613,48 +10589,42 @@
         <v>3133</v>
       </c>
       <c r="Z1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA1" t="s">
         <v>3134</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>3135</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>3136</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE1" t="s">
         <v>3137</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>3138</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>3139</v>
       </c>
-      <c r="AF1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>3140</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>3141</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>3142</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>3143</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>3145</v>
+        <v>3142</v>
       </c>
       <c r="D2" t="s">
         <v>29</v>
@@ -10708,62 +10678,60 @@
         <v>9262</v>
       </c>
       <c r="U2" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="V2" t="n">
         <v>451327</v>
       </c>
       <c r="W2" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="Y2" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z2" t="n">
         <v>-0.0770173990612234</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AA2" t="n">
         <v>0.0116508945911765</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>3146</v>
       </c>
       <c r="AD2" t="s">
         <v>32</v>
       </c>
       <c r="AE2" t="s">
-        <v>3149</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>3149</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>3150</v>
+        <v>3146</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>3147</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>3151</v>
+        <v>3148</v>
       </c>
       <c r="D3" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="E3" t="n">
         <v>9262</v>
@@ -10814,27 +10782,31 @@
         <v>12271</v>
       </c>
       <c r="U3" t="s">
-        <v>3153</v>
+        <v>3150</v>
       </c>
       <c r="V3" t="n">
         <v>453565</v>
       </c>
       <c r="W3" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="Y3" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z3" t="n">
         <v>-0.142215085053342</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AA3" t="n">
         <v>0.0246251304813029</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>46</v>
       </c>
       <c r="AD3" t="s">
         <v>32</v>
@@ -10842,34 +10814,28 @@
       <c r="AE3" t="s">
         <v>46</v>
       </c>
-      <c r="AF3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>3154</v>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>3151</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>3155</v>
+        <v>3152</v>
       </c>
       <c r="D4" t="s">
-        <v>3156</v>
+        <v>3153</v>
       </c>
       <c r="E4" t="n">
         <v>3047</v>
@@ -10920,62 +10886,60 @@
         <v>18848</v>
       </c>
       <c r="U4" t="s">
-        <v>3157</v>
+        <v>3154</v>
       </c>
       <c r="V4" t="n">
         <v>71786</v>
       </c>
       <c r="W4" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="Y4" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-0.0579628259704589</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AA4" t="n">
         <v>0.0122280489527868</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>3155</v>
       </c>
       <c r="AD4" t="s">
         <v>32</v>
       </c>
       <c r="AE4" t="s">
-        <v>3158</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>3158</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>3159</v>
+        <v>3155</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>3156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>3160</v>
+        <v>3157</v>
       </c>
       <c r="D5" t="s">
-        <v>3161</v>
+        <v>3158</v>
       </c>
       <c r="E5" t="n">
         <v>3047</v>
@@ -11026,62 +10990,60 @@
         <v>24924</v>
       </c>
       <c r="U5" t="s">
-        <v>3162</v>
+        <v>3159</v>
       </c>
       <c r="V5" t="n">
         <v>1060242</v>
       </c>
       <c r="W5" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="Y5" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z5" t="n">
         <v>0.0614465184218798</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AA5" t="n">
         <v>0.0140924818386225</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>3160</v>
       </c>
       <c r="AD5" t="s">
         <v>32</v>
       </c>
       <c r="AE5" t="s">
-        <v>3163</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>3163</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>3164</v>
+        <v>3160</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>3161</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>3165</v>
+        <v>3162</v>
       </c>
       <c r="D6" t="s">
-        <v>3166</v>
+        <v>3163</v>
       </c>
       <c r="E6" t="n">
         <v>9262</v>
@@ -11132,62 +11094,60 @@
         <v>37524</v>
       </c>
       <c r="U6" t="s">
-        <v>3167</v>
+        <v>3164</v>
       </c>
       <c r="V6" t="n">
         <v>423961</v>
       </c>
       <c r="W6" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="Y6" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z6" t="n">
         <v>0.130540987608083</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AA6" t="n">
         <v>0.035131937310408</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>3165</v>
       </c>
       <c r="AD6" t="s">
         <v>32</v>
       </c>
       <c r="AE6" t="s">
-        <v>3168</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>3168</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="s">
         <v>3165</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>3162</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>3169</v>
+        <v>3166</v>
       </c>
       <c r="D7" t="s">
-        <v>3156</v>
+        <v>3153</v>
       </c>
       <c r="E7" t="n">
         <v>9262</v>
@@ -11238,62 +11198,60 @@
         <v>18848</v>
       </c>
       <c r="U7" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="V7" t="n">
         <v>307681</v>
       </c>
       <c r="W7" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="Y7" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z7" t="n">
         <v>0.456001117015369</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AA7" t="n">
         <v>0.134515171897199</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>3168</v>
       </c>
       <c r="AD7" t="s">
         <v>32</v>
       </c>
       <c r="AE7" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>3172</v>
+        <v>3168</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>3169</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>3173</v>
+        <v>3170</v>
       </c>
       <c r="D8" t="s">
-        <v>3156</v>
+        <v>3153</v>
       </c>
       <c r="E8" t="n">
         <v>3047</v>
@@ -11344,59 +11302,57 @@
         <v>18848</v>
       </c>
       <c r="U8" t="s">
-        <v>3174</v>
+        <v>3171</v>
       </c>
       <c r="V8" t="n">
         <v>333727</v>
       </c>
       <c r="W8" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="Y8" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z8" t="n">
         <v>0.290110390570171</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AA8" t="n">
         <v>0.0900130326820185</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>3172</v>
       </c>
       <c r="AD8" t="s">
         <v>32</v>
       </c>
       <c r="AE8" t="s">
-        <v>3175</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>3175</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>3176</v>
+        <v>3172</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>3173</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>3177</v>
+        <v>3174</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
@@ -11450,62 +11406,60 @@
         <v>9262</v>
       </c>
       <c r="U9" t="s">
-        <v>3167</v>
+        <v>3164</v>
       </c>
       <c r="V9" t="n">
         <v>20978</v>
       </c>
       <c r="W9" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="Y9" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z9" t="n">
         <v>-0.0475165782521431</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AA9" t="n">
         <v>0.0154081322148282</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>3165</v>
       </c>
       <c r="AD9" t="s">
         <v>32</v>
       </c>
       <c r="AE9" t="s">
-        <v>3168</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>3168</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>3178</v>
+        <v>3165</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>3175</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>3179</v>
+        <v>3176</v>
       </c>
       <c r="D10" t="s">
-        <v>3156</v>
+        <v>3153</v>
       </c>
       <c r="E10" t="n">
         <v>9262</v>
@@ -11556,27 +11510,31 @@
         <v>18848</v>
       </c>
       <c r="U10" t="s">
-        <v>3153</v>
+        <v>3150</v>
       </c>
       <c r="V10" t="n">
         <v>448357</v>
       </c>
       <c r="W10" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="Y10" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z10" t="n">
         <v>0.204036339314145</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AA10" t="n">
         <v>0.0617972193505103</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>46</v>
       </c>
       <c r="AD10" t="s">
         <v>32</v>
@@ -11584,31 +11542,25 @@
       <c r="AE10" t="s">
         <v>46</v>
       </c>
-      <c r="AF10" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>3180</v>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>3177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>3181</v>
+        <v>3178</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
@@ -11662,62 +11614,60 @@
         <v>9262</v>
       </c>
       <c r="U11" t="s">
-        <v>3182</v>
+        <v>3179</v>
       </c>
       <c r="V11" t="n">
         <v>260554</v>
       </c>
       <c r="W11" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y11" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z11" t="n">
         <v>-0.206037835992958</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AA11" t="n">
         <v>0.0732283574783132</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>3180</v>
       </c>
       <c r="AD11" t="s">
         <v>32</v>
       </c>
       <c r="AE11" t="s">
-        <v>3183</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>3183</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>3181</v>
+        <v>3180</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>3178</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>3184</v>
+        <v>3181</v>
       </c>
       <c r="D12" t="s">
-        <v>3156</v>
+        <v>3153</v>
       </c>
       <c r="E12" t="n">
         <v>3047</v>
@@ -11768,62 +11718,60 @@
         <v>18848</v>
       </c>
       <c r="U12" t="s">
-        <v>3185</v>
+        <v>3182</v>
       </c>
       <c r="V12" t="n">
         <v>254418</v>
       </c>
       <c r="W12" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z12" t="n">
         <v>0.0547860572821387</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AA12" t="n">
         <v>0.0195981686057299</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>3183</v>
       </c>
       <c r="AD12" t="s">
         <v>32</v>
       </c>
       <c r="AE12" t="s">
-        <v>3186</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>3186</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>3184</v>
+        <v>3183</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>3181</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>3187</v>
+        <v>3184</v>
       </c>
       <c r="D13" t="s">
-        <v>3156</v>
+        <v>3153</v>
       </c>
       <c r="E13" t="n">
         <v>3047</v>
@@ -11874,59 +11822,57 @@
         <v>18848</v>
       </c>
       <c r="U13" t="s">
-        <v>3167</v>
+        <v>3164</v>
       </c>
       <c r="V13" t="n">
         <v>1057455</v>
       </c>
       <c r="W13" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
-      <c r="Y13"/>
-      <c r="Z13"/>
-      <c r="AA13" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="Y13" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z13" t="n">
         <v>0.0418770339520698</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AA13" t="n">
         <v>0.0155880000705565</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>3165</v>
       </c>
       <c r="AD13" t="s">
         <v>32</v>
       </c>
       <c r="AE13" t="s">
-        <v>3168</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>3168</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>3188</v>
+        <v>3165</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>3185</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>3189</v>
+        <v>3186</v>
       </c>
       <c r="D14" t="s">
         <v>29</v>
@@ -11980,59 +11926,57 @@
         <v>9262</v>
       </c>
       <c r="U14" t="s">
-        <v>3167</v>
+        <v>3164</v>
       </c>
       <c r="V14" t="n">
         <v>23935</v>
       </c>
       <c r="W14" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
-      <c r="Y14"/>
-      <c r="Z14"/>
-      <c r="AA14" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="Y14" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z14" t="n">
         <v>-0.0616348268276572</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AA14" t="n">
         <v>0.0256116422569783</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>3165</v>
       </c>
       <c r="AD14" t="s">
         <v>32</v>
       </c>
       <c r="AE14" t="s">
-        <v>3168</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>3168</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>3190</v>
+        <v>3165</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>3187</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>3191</v>
+        <v>3188</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
@@ -12086,59 +12030,57 @@
         <v>3047</v>
       </c>
       <c r="U15" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="V15" t="n">
         <v>310838</v>
       </c>
       <c r="W15" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AA15" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="Y15" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z15" t="n">
         <v>0.340147225436812</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AA15" t="n">
         <v>0.121423363639467</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>3168</v>
       </c>
       <c r="AD15" t="s">
         <v>32</v>
       </c>
       <c r="AE15" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>3192</v>
+        <v>3168</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>3189</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>3193</v>
+        <v>3190</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
@@ -12192,59 +12134,57 @@
         <v>3047</v>
       </c>
       <c r="U16" t="s">
-        <v>3194</v>
+        <v>3191</v>
       </c>
       <c r="V16" t="n">
         <v>450765</v>
       </c>
       <c r="W16" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="Y16" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z16" t="n">
         <v>0.14914740757284</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AA16" t="n">
         <v>0.0549259477040528</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>3192</v>
       </c>
       <c r="AD16" t="s">
         <v>32</v>
       </c>
       <c r="AE16" t="s">
-        <v>3195</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>3195</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>3196</v>
+        <v>3192</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>3193</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>3197</v>
+        <v>3194</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
@@ -12298,59 +12238,57 @@
         <v>3047</v>
       </c>
       <c r="U17" t="s">
-        <v>3167</v>
+        <v>3164</v>
       </c>
       <c r="V17" t="n">
         <v>149460</v>
       </c>
       <c r="W17" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AA17" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="Y17" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z17" t="n">
         <v>-0.144142068857882</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AA17" t="n">
         <v>0.0535925782661496</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>3165</v>
       </c>
       <c r="AD17" t="s">
         <v>32</v>
       </c>
       <c r="AE17" t="s">
-        <v>3168</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>3168</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>3198</v>
+        <v>3165</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>3195</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>3199</v>
+        <v>3196</v>
       </c>
       <c r="D18" t="s">
         <v>22</v>
@@ -12404,59 +12342,57 @@
         <v>3047</v>
       </c>
       <c r="U18" t="s">
-        <v>3200</v>
+        <v>3197</v>
       </c>
       <c r="V18" t="n">
         <v>158760</v>
       </c>
       <c r="W18" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AA18" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y18" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z18" t="n">
         <v>0.390104392929961</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AA18" t="n">
         <v>0.145405449915427</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>3198</v>
       </c>
       <c r="AD18" t="s">
         <v>32</v>
       </c>
       <c r="AE18" t="s">
-        <v>3201</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>3201</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>3202</v>
+        <v>3198</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>3199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B19" t="s">
         <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>3203</v>
+        <v>3200</v>
       </c>
       <c r="D19" t="s">
         <v>29</v>
@@ -12510,62 +12446,60 @@
         <v>9262</v>
       </c>
       <c r="U19" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="V19" t="n">
         <v>554396</v>
       </c>
       <c r="W19" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
-      <c r="Y19"/>
-      <c r="Z19"/>
-      <c r="AA19" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="Y19" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z19" t="n">
         <v>-0.231491417317421</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AA19" t="n">
         <v>0.0891083509964359</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>3146</v>
       </c>
       <c r="AD19" t="s">
         <v>32</v>
       </c>
       <c r="AE19" t="s">
-        <v>3149</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>3149</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>3204</v>
+        <v>3146</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>3201</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B20" t="s">
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>3205</v>
+        <v>3202</v>
       </c>
       <c r="D20" t="s">
-        <v>3166</v>
+        <v>3163</v>
       </c>
       <c r="E20" t="n">
         <v>3047</v>
@@ -12616,62 +12550,60 @@
         <v>37524</v>
       </c>
       <c r="U20" t="s">
-        <v>3206</v>
+        <v>3203</v>
       </c>
       <c r="V20" t="n">
         <v>22938</v>
       </c>
       <c r="W20" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
       </c>
-      <c r="Y20"/>
-      <c r="Z20"/>
-      <c r="AA20" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="Y20" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z20" t="n">
         <v>0.104112860467331</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AA20" t="n">
         <v>0.0409449060649048</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>3204</v>
       </c>
       <c r="AD20" t="s">
         <v>32</v>
       </c>
       <c r="AE20" t="s">
-        <v>3207</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>3207</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>3208</v>
+        <v>3204</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>3205</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B21" t="s">
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>3209</v>
+        <v>3206</v>
       </c>
       <c r="D21" t="s">
-        <v>3210</v>
+        <v>3207</v>
       </c>
       <c r="E21" t="n">
         <v>3047</v>
@@ -12722,62 +12654,60 @@
         <v>17061</v>
       </c>
       <c r="U21" t="s">
-        <v>3167</v>
+        <v>3164</v>
       </c>
       <c r="V21" t="n">
         <v>784127</v>
       </c>
       <c r="W21" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
       </c>
-      <c r="Y21"/>
-      <c r="Z21"/>
-      <c r="AA21" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="Y21" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z21" t="n">
         <v>0.138630103716853</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AA21" t="n">
         <v>0.0592485588553332</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>3165</v>
       </c>
       <c r="AD21" t="s">
         <v>32</v>
       </c>
       <c r="AE21" t="s">
-        <v>3168</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>3168</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>3211</v>
+        <v>3165</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>3208</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B22" t="s">
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>3212</v>
+        <v>3209</v>
       </c>
       <c r="D22" t="s">
-        <v>3213</v>
+        <v>3210</v>
       </c>
       <c r="E22" t="n">
         <v>24924</v>
@@ -12828,62 +12758,60 @@
         <v>26422</v>
       </c>
       <c r="U22" t="s">
-        <v>3200</v>
+        <v>3197</v>
       </c>
       <c r="V22" t="n">
         <v>824609</v>
       </c>
       <c r="W22" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
       </c>
-      <c r="Y22"/>
-      <c r="Z22"/>
-      <c r="AA22" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="Y22" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z22" t="n">
         <v>0.70593239505107</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AA22" t="n">
         <v>0.343618383036904</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>3198</v>
       </c>
       <c r="AD22" t="s">
         <v>32</v>
       </c>
       <c r="AE22" t="s">
-        <v>3201</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>3201</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>3212</v>
+        <v>3198</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>3209</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B23" t="s">
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>3214</v>
+        <v>3211</v>
       </c>
       <c r="D23" t="s">
-        <v>3215</v>
+        <v>3212</v>
       </c>
       <c r="E23" t="n">
         <v>24924</v>
@@ -12934,59 +12862,57 @@
         <v>31748</v>
       </c>
       <c r="U23" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="V23" t="n">
         <v>51111</v>
       </c>
       <c r="W23" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
       </c>
-      <c r="Y23"/>
-      <c r="Z23"/>
-      <c r="AA23" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="Y23" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z23" t="n">
         <v>0.121787174850645</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AA23" t="n">
         <v>0.0525229844165035</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>3146</v>
       </c>
       <c r="AD23" t="s">
         <v>32</v>
       </c>
       <c r="AE23" t="s">
-        <v>3149</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>3149</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="s">
-        <v>3216</v>
+        <v>3146</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>3213</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B24" t="s">
         <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>3217</v>
+        <v>3214</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
@@ -13040,62 +12966,60 @@
         <v>3047</v>
       </c>
       <c r="U24" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="V24" t="n">
         <v>338083</v>
       </c>
       <c r="W24" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
       </c>
-      <c r="Y24"/>
-      <c r="Z24"/>
-      <c r="AA24" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="Y24" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z24" t="n">
         <v>0.23543837863503</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AA24" t="n">
         <v>0.134016662189632</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>3146</v>
       </c>
       <c r="AD24" t="s">
         <v>32</v>
       </c>
       <c r="AE24" t="s">
-        <v>3149</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>3149</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>3218</v>
+        <v>3146</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>3215</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B25" t="s">
         <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>3219</v>
+        <v>3216</v>
       </c>
       <c r="D25" t="s">
-        <v>3213</v>
+        <v>3210</v>
       </c>
       <c r="E25" t="n">
         <v>3047</v>
@@ -13146,59 +13070,57 @@
         <v>26422</v>
       </c>
       <c r="U25" t="s">
-        <v>3182</v>
+        <v>3179</v>
       </c>
       <c r="V25" t="n">
         <v>322686</v>
       </c>
       <c r="W25" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
       </c>
-      <c r="Y25"/>
-      <c r="Z25"/>
-      <c r="AA25" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="Y25" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z25" t="n">
         <v>-0.14528461881362</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AA25" t="n">
         <v>0.0603514204126171</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>3180</v>
       </c>
       <c r="AD25" t="s">
         <v>32</v>
       </c>
       <c r="AE25" t="s">
-        <v>3183</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>3183</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>3220</v>
+        <v>3180</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>3217</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B26" t="s">
         <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>3221</v>
+        <v>3218</v>
       </c>
       <c r="D26" t="s">
         <v>22</v>
@@ -13252,62 +13174,60 @@
         <v>3047</v>
       </c>
       <c r="U26" t="s">
-        <v>3174</v>
+        <v>3171</v>
       </c>
       <c r="V26" t="n">
         <v>255115</v>
       </c>
       <c r="W26" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X26" t="b">
         <v>1</v>
       </c>
-      <c r="Y26"/>
-      <c r="Z26"/>
-      <c r="AA26" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="Y26" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z26" t="n">
         <v>-0.0524521060383855</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AA26" t="n">
         <v>0.0219695479750746</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>3172</v>
       </c>
       <c r="AD26" t="s">
         <v>32</v>
       </c>
       <c r="AE26" t="s">
-        <v>3175</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>3175</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>3222</v>
+        <v>3172</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>3219</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B27" t="s">
         <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>3223</v>
+        <v>3220</v>
       </c>
       <c r="D27" t="s">
-        <v>3156</v>
+        <v>3153</v>
       </c>
       <c r="E27" t="n">
         <v>3047</v>
@@ -13358,48 +13278,46 @@
         <v>18848</v>
       </c>
       <c r="U27" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="V27" t="n">
         <v>73285</v>
       </c>
       <c r="W27" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
       </c>
-      <c r="Y27"/>
-      <c r="Z27"/>
-      <c r="AA27" t="s">
-        <v>3148</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="Y27" t="s">
+        <v>3145</v>
+      </c>
+      <c r="Z27" t="n">
         <v>0.0792625489545239</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AA27" t="n">
         <v>0.03349001721143</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>3168</v>
       </c>
       <c r="AD27" t="s">
         <v>32</v>
       </c>
       <c r="AE27" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>3171</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>3224</v>
+        <v>3168</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>3221</v>
       </c>
     </row>
   </sheetData>
@@ -13478,37 +13396,28 @@
         <v>3131</v>
       </c>
       <c r="V1" t="s">
-        <v>3225</v>
+        <v>126</v>
       </c>
       <c r="W1" t="s">
-        <v>3226</v>
+        <v>3134</v>
       </c>
       <c r="X1" t="s">
-        <v>3227</v>
+        <v>3135</v>
       </c>
       <c r="Y1" t="s">
-        <v>3228</v>
+        <v>3136</v>
       </c>
       <c r="Z1" t="s">
-        <v>3229</v>
+        <v>31</v>
       </c>
       <c r="AA1" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="AB1" t="s">
-        <v>3139</v>
+        <v>3222</v>
       </c>
       <c r="AC1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD1" t="s">
         <v>3140</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>3230</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>3143</v>
       </c>
     </row>
     <row r="2">
@@ -13516,10 +13425,10 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>3231</v>
+        <v>3223</v>
       </c>
       <c r="C2" t="s">
-        <v>3232</v>
+        <v>3224</v>
       </c>
       <c r="D2" t="n">
         <v>3047</v>
@@ -13576,37 +13485,28 @@
         <v>8971</v>
       </c>
       <c r="V2" t="n">
-        <v>7.4543813227153</v>
+        <v>0.211891139126091</v>
       </c>
       <c r="W2" t="n">
-        <v>6.15781076785049</v>
-      </c>
-      <c r="X2" t="n">
-        <v>5.14398279375473</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.7249127826857</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.24217334304476</v>
+        <v>0.0409252430132426</v>
+      </c>
+      <c r="X2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>32</v>
       </c>
       <c r="AA2" t="s">
         <v>32</v>
       </c>
-      <c r="AB2" t="s">
-        <v>32</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>3233</v>
+        <v>3225</v>
       </c>
     </row>
     <row r="3">
@@ -13614,10 +13514,10 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>3234</v>
+        <v>3226</v>
       </c>
       <c r="C3" t="s">
-        <v>3166</v>
+        <v>3163</v>
       </c>
       <c r="D3" t="n">
         <v>24924</v>
@@ -13674,37 +13574,28 @@
         <v>36579</v>
       </c>
       <c r="V3" t="n">
-        <v>-6.00046257018101</v>
+        <v>-0.529137706311557</v>
       </c>
       <c r="W3" t="n">
-        <v>-5.47180803893852</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-4.55893395254635</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-4.13352654244907</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-3.98376443725894</v>
+        <v>0.107283491796412</v>
+      </c>
+      <c r="X3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>32</v>
       </c>
       <c r="AA3" t="s">
         <v>32</v>
       </c>
-      <c r="AB3" t="s">
-        <v>32</v>
+      <c r="AB3" t="n">
+        <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>3235</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="4">
@@ -13712,7 +13603,7 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>3236</v>
+        <v>3228</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
@@ -13772,37 +13663,28 @@
         <v>6107</v>
       </c>
       <c r="V4" t="n">
-        <v>1.94854979169145</v>
+        <v>0.785905197717854</v>
       </c>
       <c r="W4" t="n">
-        <v>3.74939186327013</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.82648126276657</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>4.35842600477422</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.20711722945569</v>
+        <v>0.264656579285953</v>
+      </c>
+      <c r="X4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>32</v>
       </c>
       <c r="AA4" t="s">
         <v>32</v>
       </c>
-      <c r="AB4" t="s">
-        <v>32</v>
+      <c r="AB4" t="n">
+        <v>0</v>
       </c>
       <c r="AC4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>3237</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="5">
@@ -13810,10 +13692,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>3238</v>
+        <v>3230</v>
       </c>
       <c r="C5" t="s">
-        <v>3239</v>
+        <v>3231</v>
       </c>
       <c r="D5" t="n">
         <v>52588</v>
@@ -13870,37 +13752,28 @@
         <v>63810</v>
       </c>
       <c r="V5" t="n">
-        <v>4.27798290547164</v>
+        <v>0.192440471323959</v>
       </c>
       <c r="W5" t="n">
-        <v>2.56424472316997</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.27461324126819</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.97018647041789</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.12742852645045</v>
+        <v>0.0576867061850896</v>
+      </c>
+      <c r="X5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>32</v>
       </c>
       <c r="AA5" t="s">
         <v>32</v>
       </c>
-      <c r="AB5" t="s">
-        <v>32</v>
+      <c r="AB5" t="n">
+        <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>3240</v>
+        <v>3232</v>
       </c>
     </row>
     <row r="6">
@@ -13908,10 +13781,10 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>3241</v>
+        <v>3233</v>
       </c>
       <c r="C6" t="s">
-        <v>3242</v>
+        <v>3234</v>
       </c>
       <c r="D6" t="n">
         <v>42355</v>
@@ -13968,37 +13841,28 @@
         <v>39163</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.38637265993442</v>
+        <v>-0.161979214489972</v>
       </c>
       <c r="W6" t="n">
-        <v>-3.13967444156104</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-3.31382743729042</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-1.48998661274468</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-2.7162450411456</v>
+        <v>0.0560516849325641</v>
+      </c>
+      <c r="X6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>32</v>
       </c>
       <c r="AA6" t="s">
         <v>32</v>
       </c>
-      <c r="AB6" t="s">
-        <v>32</v>
+      <c r="AB6" t="n">
+        <v>0</v>
       </c>
       <c r="AC6" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>3243</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="7">
@@ -14006,10 +13870,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>3244</v>
+        <v>3236</v>
       </c>
       <c r="C7" t="s">
-        <v>3245</v>
+        <v>3237</v>
       </c>
       <c r="D7" t="n">
         <v>42355</v>
@@ -14066,37 +13930,28 @@
         <v>42303</v>
       </c>
       <c r="V7" t="n">
-        <v>0.961186987012996</v>
+        <v>0.178882397661341</v>
       </c>
       <c r="W7" t="n">
-        <v>3.91364617527035</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.35906569260413</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.751679368727</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.38571472935212</v>
+        <v>0.0733459654583936</v>
+      </c>
+      <c r="X7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>32</v>
       </c>
       <c r="AA7" t="s">
         <v>32</v>
       </c>
-      <c r="AB7" t="s">
-        <v>32</v>
+      <c r="AB7" t="n">
+        <v>0</v>
       </c>
       <c r="AC7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>3246</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="8">
@@ -14104,10 +13959,10 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>3247</v>
+        <v>3239</v>
       </c>
       <c r="C8" t="s">
-        <v>3248</v>
+        <v>3240</v>
       </c>
       <c r="D8" t="n">
         <v>258195</v>
@@ -14164,37 +14019,28 @@
         <v>50051</v>
       </c>
       <c r="V8" t="n">
-        <v>0.811609216022041</v>
+        <v>-0.0284945145243722</v>
       </c>
       <c r="W8" t="n">
-        <v>-2.34324065015604</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1.97066797258914</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-1.08248893606091</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.36809412786676</v>
+        <v>0.0795816750150964</v>
+      </c>
+      <c r="X8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>32</v>
       </c>
       <c r="AA8" t="s">
         <v>32</v>
       </c>
-      <c r="AB8" t="s">
-        <v>32</v>
+      <c r="AB8" t="n">
+        <v>0.0211037682845408</v>
       </c>
       <c r="AC8" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.0211037682845408</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>3249</v>
+        <v>3241</v>
       </c>
     </row>
   </sheetData>
@@ -14225,34 +14071,34 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>3250</v>
+        <v>3242</v>
       </c>
       <c r="G1" t="s">
         <v>1625</v>
       </c>
       <c r="H1" t="s">
-        <v>3251</v>
+        <v>3243</v>
       </c>
       <c r="I1" t="s">
-        <v>3252</v>
+        <v>3244</v>
       </c>
       <c r="J1" t="s">
         <v>1683</v>
       </c>
       <c r="K1" t="s">
-        <v>3253</v>
+        <v>3245</v>
       </c>
       <c r="L1" t="s">
-        <v>3254</v>
+        <v>3246</v>
       </c>
       <c r="M1" t="s">
-        <v>3255</v>
+        <v>3247</v>
       </c>
       <c r="N1" t="s">
-        <v>3256</v>
+        <v>3248</v>
       </c>
       <c r="O1" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="P1" t="s">
         <v>3131</v>
@@ -14272,33 +14118,33 @@
         <v>372</v>
       </c>
       <c r="E2" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F2" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G2" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>3260</v>
+        <v>3252</v>
       </c>
       <c r="K2" t="s">
-        <v>3261</v>
+        <v>3253</v>
       </c>
       <c r="L2" t="s">
-        <v>3260</v>
+        <v>3252</v>
       </c>
       <c r="M2" t="s">
-        <v>3262</v>
+        <v>3254</v>
       </c>
       <c r="N2" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O2" t="s">
-        <v>3264</v>
+        <v>3256</v>
       </c>
       <c r="P2" t="n">
         <v>1996</v>
@@ -14318,30 +14164,30 @@
         <v>2118</v>
       </c>
       <c r="E3" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F3" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G3" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>3265</v>
+        <v>3257</v>
       </c>
       <c r="K3" t="s">
-        <v>3266</v>
+        <v>3258</v>
       </c>
       <c r="L3" t="s">
-        <v>3265</v>
+        <v>3257</v>
       </c>
       <c r="M3" t="s">
-        <v>3262</v>
+        <v>3254</v>
       </c>
       <c r="N3" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O3"/>
       <c r="P3" t="n">
@@ -14362,33 +14208,33 @@
         <v>1422</v>
       </c>
       <c r="E4" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="F4" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G4" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>3236</v>
+        <v>3228</v>
       </c>
       <c r="K4" t="s">
-        <v>3268</v>
+        <v>3260</v>
       </c>
       <c r="L4" t="s">
-        <v>3236</v>
+        <v>3228</v>
       </c>
       <c r="M4" t="s">
-        <v>3269</v>
+        <v>3261</v>
       </c>
       <c r="N4" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O4" t="s">
-        <v>3237</v>
+        <v>3229</v>
       </c>
       <c r="P4" t="n">
         <v>6818</v>
@@ -14408,33 +14254,33 @@
         <v>2136</v>
       </c>
       <c r="E5" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F5" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G5" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>3231</v>
+        <v>3223</v>
       </c>
       <c r="K5" t="s">
-        <v>3270</v>
+        <v>3262</v>
       </c>
       <c r="L5" t="s">
-        <v>3231</v>
+        <v>3223</v>
       </c>
       <c r="M5" t="s">
-        <v>3271</v>
+        <v>3263</v>
       </c>
       <c r="N5" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O5" t="s">
-        <v>3233</v>
+        <v>3225</v>
       </c>
       <c r="P5" t="n">
         <v>10158</v>
@@ -14454,33 +14300,33 @@
         <v>1224</v>
       </c>
       <c r="E6" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="F6" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G6" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6" t="s">
-        <v>3272</v>
+        <v>3264</v>
       </c>
       <c r="K6" t="s">
-        <v>3273</v>
+        <v>3265</v>
       </c>
       <c r="L6" t="s">
-        <v>3272</v>
+        <v>3264</v>
       </c>
       <c r="M6" t="s">
-        <v>3274</v>
+        <v>3266</v>
       </c>
       <c r="N6" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O6" t="s">
-        <v>3275</v>
+        <v>3267</v>
       </c>
       <c r="P6" t="n">
         <v>15096</v>
@@ -14500,33 +14346,33 @@
         <v>981</v>
       </c>
       <c r="E7" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F7" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G7" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>3276</v>
+        <v>3268</v>
       </c>
       <c r="K7" t="s">
-        <v>3277</v>
+        <v>3269</v>
       </c>
       <c r="L7" t="s">
-        <v>3276</v>
+        <v>3268</v>
       </c>
       <c r="M7" t="s">
-        <v>3278</v>
+        <v>3270</v>
       </c>
       <c r="N7" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O7" t="s">
-        <v>3279</v>
+        <v>3271</v>
       </c>
       <c r="P7" t="n">
         <v>17849</v>
@@ -14546,33 +14392,33 @@
         <v>1851</v>
       </c>
       <c r="E8" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="F8" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G8" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="K8" t="s">
-        <v>3281</v>
+        <v>3273</v>
       </c>
       <c r="L8" t="s">
-        <v>3280</v>
+        <v>3272</v>
       </c>
       <c r="M8" t="s">
-        <v>3282</v>
+        <v>3274</v>
       </c>
       <c r="N8" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O8" t="s">
-        <v>3283</v>
+        <v>3275</v>
       </c>
       <c r="P8" t="n">
         <v>23159</v>
@@ -14592,33 +14438,33 @@
         <v>945</v>
       </c>
       <c r="E9" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="F9" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G9" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9" t="s">
-        <v>3284</v>
+        <v>3276</v>
       </c>
       <c r="K9" t="s">
-        <v>3285</v>
+        <v>3277</v>
       </c>
       <c r="L9" t="s">
-        <v>3284</v>
+        <v>3276</v>
       </c>
       <c r="M9" t="s">
-        <v>3286</v>
+        <v>3278</v>
       </c>
       <c r="N9" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O9" t="s">
-        <v>3287</v>
+        <v>3279</v>
       </c>
       <c r="P9" t="n">
         <v>25687</v>
@@ -14638,33 +14484,33 @@
         <v>3861</v>
       </c>
       <c r="E10" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F10" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G10" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>3288</v>
+        <v>3280</v>
       </c>
       <c r="K10" t="s">
-        <v>3289</v>
+        <v>3281</v>
       </c>
       <c r="L10" t="s">
-        <v>3288</v>
+        <v>3280</v>
       </c>
       <c r="M10" t="s">
-        <v>3290</v>
+        <v>3282</v>
       </c>
       <c r="N10" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O10" t="s">
-        <v>3291</v>
+        <v>3283</v>
       </c>
       <c r="P10" t="n">
         <v>28757</v>
@@ -14684,33 +14530,33 @@
         <v>612</v>
       </c>
       <c r="E11" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F11" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G11" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>3292</v>
+        <v>3284</v>
       </c>
       <c r="K11" t="s">
-        <v>3293</v>
+        <v>3285</v>
       </c>
       <c r="L11" t="s">
-        <v>3292</v>
+        <v>3284</v>
       </c>
       <c r="M11" t="s">
-        <v>3294</v>
+        <v>3286</v>
       </c>
       <c r="N11" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O11" t="s">
-        <v>3295</v>
+        <v>3287</v>
       </c>
       <c r="P11" t="n">
         <v>31388</v>
@@ -14730,33 +14576,33 @@
         <v>2148</v>
       </c>
       <c r="E12" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F12" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G12" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12" t="s">
-        <v>3296</v>
+        <v>3288</v>
       </c>
       <c r="K12" t="s">
-        <v>3297</v>
+        <v>3289</v>
       </c>
       <c r="L12" t="s">
-        <v>3296</v>
+        <v>3288</v>
       </c>
       <c r="M12" t="s">
-        <v>3298</v>
+        <v>3290</v>
       </c>
       <c r="N12" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O12" t="s">
-        <v>3299</v>
+        <v>3291</v>
       </c>
       <c r="P12" t="n">
         <v>33034</v>
@@ -14776,33 +14622,33 @@
         <v>1872</v>
       </c>
       <c r="E13" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="F13" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G13" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>3300</v>
+        <v>3292</v>
       </c>
       <c r="K13" t="s">
-        <v>3301</v>
+        <v>3293</v>
       </c>
       <c r="L13" t="s">
-        <v>3300</v>
+        <v>3292</v>
       </c>
       <c r="M13" t="s">
-        <v>3302</v>
+        <v>3294</v>
       </c>
       <c r="N13" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O13" t="s">
-        <v>3303</v>
+        <v>3295</v>
       </c>
       <c r="P13" t="n">
         <v>35478</v>
@@ -14822,33 +14668,33 @@
         <v>1455</v>
       </c>
       <c r="E14" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F14" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G14" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" t="s">
-        <v>3234</v>
+        <v>3226</v>
       </c>
       <c r="K14" t="s">
-        <v>3304</v>
+        <v>3296</v>
       </c>
       <c r="L14" t="s">
-        <v>3234</v>
+        <v>3226</v>
       </c>
       <c r="M14" t="s">
-        <v>3305</v>
+        <v>3297</v>
       </c>
       <c r="N14" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O14" t="s">
-        <v>3235</v>
+        <v>3227</v>
       </c>
       <c r="P14" t="n">
         <v>37426</v>
@@ -14868,33 +14714,33 @@
         <v>3075</v>
       </c>
       <c r="E15" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="F15" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G15" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>3241</v>
+        <v>3233</v>
       </c>
       <c r="K15" t="s">
-        <v>3306</v>
+        <v>3298</v>
       </c>
       <c r="L15" t="s">
-        <v>3241</v>
+        <v>3233</v>
       </c>
       <c r="M15" t="s">
-        <v>3307</v>
+        <v>3299</v>
       </c>
       <c r="N15" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O15" t="s">
-        <v>3243</v>
+        <v>3235</v>
       </c>
       <c r="P15" t="n">
         <v>40700</v>
@@ -14914,33 +14760,33 @@
         <v>3873</v>
       </c>
       <c r="E16" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F16" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G16" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" t="s">
-        <v>3244</v>
+        <v>3236</v>
       </c>
       <c r="K16" t="s">
-        <v>3308</v>
+        <v>3300</v>
       </c>
       <c r="L16" t="s">
-        <v>3244</v>
+        <v>3236</v>
       </c>
       <c r="M16" t="s">
-        <v>3309</v>
+        <v>3301</v>
       </c>
       <c r="N16" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O16" t="s">
-        <v>3246</v>
+        <v>3238</v>
       </c>
       <c r="P16" t="n">
         <v>44359</v>
@@ -14960,33 +14806,33 @@
         <v>816</v>
       </c>
       <c r="E17" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="F17" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G17" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" t="s">
-        <v>3310</v>
+        <v>3302</v>
       </c>
       <c r="K17" t="s">
-        <v>3311</v>
+        <v>3303</v>
       </c>
       <c r="L17" t="s">
-        <v>3310</v>
+        <v>3302</v>
       </c>
       <c r="M17" t="s">
-        <v>3312</v>
+        <v>3304</v>
       </c>
       <c r="N17" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O17" t="s">
-        <v>3313</v>
+        <v>3305</v>
       </c>
       <c r="P17" t="n">
         <v>47564</v>
@@ -15006,33 +14852,33 @@
         <v>762</v>
       </c>
       <c r="E18" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="F18" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G18" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" t="s">
-        <v>3314</v>
+        <v>3306</v>
       </c>
       <c r="K18" t="s">
-        <v>3315</v>
+        <v>3307</v>
       </c>
       <c r="L18" t="s">
-        <v>3314</v>
+        <v>3306</v>
       </c>
       <c r="M18" t="s">
-        <v>3316</v>
+        <v>3308</v>
       </c>
       <c r="N18" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O18" t="s">
-        <v>3317</v>
+        <v>3309</v>
       </c>
       <c r="P18" t="n">
         <v>48574</v>
@@ -15052,33 +14898,33 @@
         <v>804</v>
       </c>
       <c r="E19" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F19" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G19" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>3318</v>
+        <v>3310</v>
       </c>
       <c r="K19" t="s">
-        <v>3319</v>
+        <v>3311</v>
       </c>
       <c r="L19" t="s">
-        <v>3318</v>
+        <v>3310</v>
       </c>
       <c r="M19" t="s">
-        <v>3320</v>
+        <v>3312</v>
       </c>
       <c r="N19" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O19" t="s">
-        <v>3321</v>
+        <v>3313</v>
       </c>
       <c r="P19" t="n">
         <v>49408</v>
@@ -15098,33 +14944,33 @@
         <v>3303</v>
       </c>
       <c r="E20" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="F20" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G20" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" t="s">
-        <v>3247</v>
+        <v>3239</v>
       </c>
       <c r="K20" t="s">
-        <v>3322</v>
+        <v>3314</v>
       </c>
       <c r="L20" t="s">
-        <v>3247</v>
+        <v>3239</v>
       </c>
       <c r="M20" t="s">
-        <v>3323</v>
+        <v>3315</v>
       </c>
       <c r="N20" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O20" t="s">
-        <v>3249</v>
+        <v>3241</v>
       </c>
       <c r="P20" t="n">
         <v>51702</v>
@@ -15144,33 +14990,33 @@
         <v>1899</v>
       </c>
       <c r="E21" t="s">
-        <v>3267</v>
+        <v>3259</v>
       </c>
       <c r="F21" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G21" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" t="s">
-        <v>3324</v>
+        <v>3316</v>
       </c>
       <c r="K21" t="s">
-        <v>3325</v>
+        <v>3317</v>
       </c>
       <c r="L21" t="s">
-        <v>3324</v>
+        <v>3316</v>
       </c>
       <c r="M21" t="s">
-        <v>3326</v>
+        <v>3318</v>
       </c>
       <c r="N21" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O21" t="s">
-        <v>3327</v>
+        <v>3319</v>
       </c>
       <c r="P21" t="n">
         <v>54653</v>
@@ -15190,13 +15036,13 @@
         <v>7425</v>
       </c>
       <c r="E22" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F22" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G22" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
@@ -15204,16 +15050,16 @@
         <v>99</v>
       </c>
       <c r="K22" t="s">
-        <v>3328</v>
+        <v>3320</v>
       </c>
       <c r="L22" t="s">
         <v>99</v>
       </c>
       <c r="M22" t="s">
-        <v>3329</v>
+        <v>3321</v>
       </c>
       <c r="N22" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O22" t="s">
         <v>100</v>
@@ -15236,33 +15082,33 @@
         <v>3537</v>
       </c>
       <c r="E23" t="s">
-        <v>3258</v>
+        <v>3250</v>
       </c>
       <c r="F23" t="s">
-        <v>3259</v>
+        <v>3251</v>
       </c>
       <c r="G23" t="s">
-        <v>3257</v>
+        <v>3249</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23" t="s">
-        <v>3238</v>
+        <v>3230</v>
       </c>
       <c r="K23" t="s">
-        <v>3330</v>
+        <v>3322</v>
       </c>
       <c r="L23" t="s">
-        <v>3238</v>
+        <v>3230</v>
       </c>
       <c r="M23" t="s">
-        <v>3331</v>
+        <v>3323</v>
       </c>
       <c r="N23" t="s">
-        <v>3263</v>
+        <v>3255</v>
       </c>
       <c r="O23" t="s">
-        <v>3240</v>
+        <v>3232</v>
       </c>
       <c r="P23" t="n">
         <v>65698</v>
@@ -47218,10 +47064,10 @@
         <v>0.000020132653159247</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000244368789973208</v>
+        <v>0.000257944833860608</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000171486870156637</v>
+        <v>0.00018577744266969</v>
       </c>
       <c r="J2" t="s">
         <v>1698</v>
@@ -47253,10 +47099,10 @@
         <v>0.0000271520877748009</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000244368789973208</v>
+        <v>0.000257944833860608</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000171486870156637</v>
+        <v>0.00018577744266969</v>
       </c>
       <c r="J3" t="s">
         <v>1704</v>
@@ -47285,13 +47131,13 @@
         <v>1708</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000854949444329524</v>
+        <v>0.000983115129476192</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00490080620196652</v>
+        <v>0.00517307321318688</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00343916224699405</v>
+        <v>0.00372575910091022</v>
       </c>
       <c r="J4" t="s">
         <v>1709</v>
@@ -47323,10 +47169,10 @@
         <v>0.00108906804488145</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00490080620196652</v>
+        <v>0.00517307321318688</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00343916224699405</v>
+        <v>0.00372575910091022</v>
       </c>
       <c r="J5" t="s">
         <v>1713</v>
@@ -47358,10 +47204,10 @@
         <v>0.00271238230610306</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009764576301971</v>
+        <v>0.0103070527631916</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00685233424699719</v>
+        <v>0.00742336210091363</v>
       </c>
       <c r="J6" t="s">
         <v>1719</v>
@@ -47393,10 +47239,10 @@
         <v>0.00957550789742525</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0287265236922757</v>
+        <v>0.0303224416751799</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0201589639945795</v>
+        <v>0.0218388776607944</v>
       </c>
       <c r="J7" t="s">
         <v>1723</v>
